--- a/Demo/lf-integrated-sch-sth/demo_lf_tas_sth_9999_2_part.xlsx
+++ b/Demo/lf-integrated-sch-sth/demo_lf_tas_sth_9999_2_part.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\lf-integrated-sch-sth\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53D8ED9B-E370-4FF5-9BF7-45A469045FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94DB4C2C-D8B9-4587-B291-5648922F912C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -630,9 +630,6 @@
     <t>once(if(${last-saved#p_index_cur}!=null,${last-saved#p_index_cur}, 0))</t>
   </si>
   <si>
-    <t>${p_index_init} + indexed-repeat(${position}, ${pi999}, count(${pi999}))</t>
-  </si>
-  <si>
     <t>sh999</t>
   </si>
   <si>
@@ -640,6 +637,9 @@
   </si>
   <si>
     <t>(Demo) 2. TAS/STH LF-ONCHO LF Participant From</t>
+  </si>
+  <si>
+    <t>${p_index_init} + indexed-repeat(${position}, ${sh999}, count(${sh999}))</t>
   </si>
 </sst>
 </file>
@@ -1602,7 +1602,7 @@
         <v>64</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>107</v>
@@ -2487,7 +2487,7 @@
         <v>102</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J57" s="10"/>
       <c r="K57" s="10"/>
@@ -2812,10 +2812,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C2" t="s">
         <v>48</v>
